--- a/data/Jain_Leads_Verified_Photos_HD.xlsx
+++ b/data/Jain_Leads_Verified_Photos_HD.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,8 +106,14 @@
       <color rgb="00334155"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -150,6 +156,12 @@
         <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -177,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,6 +233,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -862,10 +877,10 @@
         </is>
       </c>
       <c r="X2" s="11" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="12" t="inlineStr">
-        <is>
-          <t>Ready to Submit</t>
+      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Z2" s="17" t="inlineStr">
+        <is>
+          <t>Failed: Page.wait_for_selector: Timeou</t>
         </is>
       </c>
     </row>
@@ -2633,11 +2648,19 @@
           <t>Verified Jain Mandir / Derasar</t>
         </is>
       </c>
-      <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="12" t="inlineStr">
-        <is>
-          <t>Ready to Submit</t>
+      <c r="X17" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00253</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z17" s="13" t="inlineStr">
+        <is>
+          <t>Submitted - Live</t>
         </is>
       </c>
     </row>
@@ -2749,11 +2772,19 @@
           <t>Verified Jain Mandir / Derasar</t>
         </is>
       </c>
-      <c r="X18" s="4" t="inlineStr"/>
-      <c r="Y18" s="4" t="inlineStr"/>
-      <c r="Z18" s="12" t="inlineStr">
-        <is>
-          <t>Ready to Submit</t>
+      <c r="X18" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00254</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z18" s="13" t="inlineStr">
+        <is>
+          <t>Submitted - Live</t>
         </is>
       </c>
     </row>
@@ -2865,11 +2896,19 @@
           <t>Verified Jain Trust / Dharamshala</t>
         </is>
       </c>
-      <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="12" t="inlineStr">
-        <is>
-          <t>Ready to Submit</t>
+      <c r="X19" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00255</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z19" s="13" t="inlineStr">
+        <is>
+          <t>Submitted - Live</t>
         </is>
       </c>
     </row>
@@ -2981,11 +3020,19 @@
           <t>Verified Jain Mandir / Derasar</t>
         </is>
       </c>
-      <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="12" t="inlineStr">
-        <is>
-          <t>Ready to Submit</t>
+      <c r="X20" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00256</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z20" s="13" t="inlineStr">
+        <is>
+          <t>Submitted - Live</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3084,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y16" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y20" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Jain_Leads_Verified_Photos_HD.xlsx
+++ b/data/Jain_Leads_Verified_Photos_HD.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="JainForJain Data Entry Leads" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Executive Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Search &amp; Coverage Tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JainForJain Data Entry Leads'!$A$1:$Z$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JainForJain Data Entry Leads'!$A$1:$Z$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,13 +82,23 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00166534"/>
+      <color rgb="001E40AF"/>
       <sz val="9"/>
     </font>
     <font>
@@ -113,7 +124,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -140,14 +151,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FEF3C7"/>
         <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -189,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -230,10 +247,19 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -601,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -610,7 +636,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="36" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -619,14 +645,14 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
@@ -764,7 +790,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
@@ -775,7 +801,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -790,10 +816,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>+91 1412367535</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
+          <t>1412367535</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>info.tanishqjeweller@gmail.com</t>
+        </is>
+      </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Pilani Bhawan, Mirza Ismail Rd, opposite Niros, Jayanti Market, New Colony, Jaipur, Rajasthan 302001</t>
@@ -839,14 +869,14 @@
           <t>Visit Website</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R2" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S2" s="8" t="inlineStr">
@@ -856,7 +886,7 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>🏷️ View Web Logo</t>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U2" s="9" t="inlineStr">
@@ -876,15 +906,23 @@
           <t>Category Correlation</t>
         </is>
       </c>
-      <c r="X2" s="11" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="17" t="inlineStr">
-        <is>
-          <t>Failed: Page.wait_for_selector: Timeou</t>
+      <c r="X2" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00260</t>
+        </is>
+      </c>
+      <c r="Y2" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z2" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
@@ -895,7 +933,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -910,10 +948,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>+91 9772290045</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
+          <t>9772290045</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>info.jainmahaveerjew@gmail.com</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Monika Vihar, Mangyawas Rd, Shiv Choudhary Nagar, Manyawas, Mohru Nagar, Mansrovar, Jaipur, Rajasthan 302020</t>
@@ -954,15 +996,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q3" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R3" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S3" s="8" t="inlineStr">
@@ -970,9 +1016,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U3" s="9" t="inlineStr">
@@ -982,7 +1028,7 @@
 We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09772290045 or visit our premises at Monika Vihar, Mangyawas Rd, Shiv Choudhary Nagar, Manyawas, Mohru Nagar, Mansrovar, Jaipur, Rajasthan 302020.</t>
         </is>
       </c>
-      <c r="V3" s="13" t="inlineStr">
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -992,15 +1038,23 @@
           <t>Direct Name Match ('Jain')</t>
         </is>
       </c>
-      <c r="X3" s="11" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="X3" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00258</t>
+        </is>
+      </c>
+      <c r="Y3" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z3" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
@@ -1011,7 +1065,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -1026,10 +1080,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>+91 9057271383</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
+          <t>9057271383</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>info.jineshjainjewel@gmail.com</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>207-208, Johri Bazar, Ramganj Bazar, Jaipur, Rajasthan 302003</t>
@@ -1070,15 +1128,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S4" s="8" t="inlineStr">
@@ -1086,9 +1148,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U4" s="9" t="inlineStr">
@@ -1098,7 +1160,7 @@
 We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09057271383 or visit our premises at 207-208, Johri Bazar, Ramganj Bazar, Jaipur, Rajasthan 302003.</t>
         </is>
       </c>
-      <c r="V4" s="13" t="inlineStr">
+      <c r="V4" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -1108,15 +1170,23 @@
           <t>Direct Name Match ('Jain')</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="X4" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00259</t>
+        </is>
+      </c>
+      <c r="Y4" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z4" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
@@ -1127,7 +1197,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1142,10 +1212,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>+91 9636653328</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+          <t>9636653328</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>info.tijariyajainjew@gmail.com</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>38/18, Madhyam Marg, Kiran Path, Mansarovar Sector 3, Mansarovar, Jaipur, Rajasthan 302020</t>
@@ -1186,15 +1260,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P5" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S5" s="8" t="inlineStr">
@@ -1202,9 +1280,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U5" s="9" t="inlineStr">
@@ -1214,7 +1292,7 @@
 We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09636653328 or visit our premises at 38/18, Madhyam Marg, Kiran Path, Mansarovar Sector 3, Mansarovar, Jaipur, Rajasthan 302020.</t>
         </is>
       </c>
-      <c r="V5" s="13" t="inlineStr">
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -1224,15 +1302,23 @@
           <t>Direct Name Match ('Jain')</t>
         </is>
       </c>
-      <c r="X5" s="11" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="X5" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00261</t>
+        </is>
+      </c>
+      <c r="Y5" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z5" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
@@ -1243,7 +1329,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1258,10 +1344,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>+91 8478888888</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
+          <t>8478888888</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>info.jhalanijeweller@gmail.com</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Shop No, 44, Gopal Ji Ka Rasta, Tripolia Bazar, Pink City, Jaipur, Rajasthan 302003</t>
@@ -1307,14 +1397,14 @@
           <t>Visit Website</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S6" s="8" t="inlineStr">
@@ -1324,7 +1414,7 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>🏷️ View Web Logo</t>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U6" s="9" t="inlineStr">
@@ -1344,15 +1434,23 @@
           <t>Category Correlation</t>
         </is>
       </c>
-      <c r="X6" s="11" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="X6" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00262</t>
+        </is>
+      </c>
+      <c r="Y6" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z6" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
@@ -1363,7 +1461,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1378,10 +1476,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>+91 9782981032</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
+          <t>9782981032</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>info.jainjewelsbyans@gmail.com</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>13, near Brij Bal Mandir School, Vasudev Puri, B, Jhotwara, Jaipur, Rajasthan 302012</t>
@@ -1427,14 +1529,14 @@
           <t>Visit Website</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
@@ -1442,9 +1544,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U7" s="9" t="inlineStr">
@@ -1454,7 +1556,7 @@
 We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09782981032 or visit our premises at 13, near Brij Bal Mandir School, Vasudev Puri, B, Jhotwara, Jaipur, Rajasthan 302012.</t>
         </is>
       </c>
-      <c r="V7" s="13" t="inlineStr">
+      <c r="V7" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -1464,15 +1566,23 @@
           <t>Direct Name Match ('Jain')</t>
         </is>
       </c>
-      <c r="X7" s="11" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="X7" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00263</t>
+        </is>
+      </c>
+      <c r="Y7" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z7" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
@@ -1483,7 +1593,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1498,10 +1608,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>+91 9001208888</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
+          <t>9001208888</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>info.jkjsonsjeweller@gmail.com</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Dugar Building, Mirza Ismail Rd, Jaipur, Rajasthan 302001</t>
@@ -1547,14 +1661,14 @@
           <t>Visit Website</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
@@ -1564,7 +1678,7 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>🏷️ View Web Logo</t>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U8" s="9" t="inlineStr">
@@ -1584,15 +1698,23 @@
           <t>Category Correlation</t>
         </is>
       </c>
-      <c r="X8" s="11" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="X8" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00264</t>
+        </is>
+      </c>
+      <c r="Y8" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z8" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
@@ -1603,7 +1725,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1618,10 +1740,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>+91 9829829518</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
+          <t>9829829518</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>info.jaishreejewelle@gmail.com</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Poonam market, Bus Stop, Near, Panchyawala, Jaipur, Rajasthan 302034</t>
@@ -1667,14 +1793,14 @@
           <t>Visit Website</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R9" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
@@ -1684,7 +1810,7 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>🏷️ View Web Logo</t>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U9" s="9" t="inlineStr">
@@ -1704,15 +1830,23 @@
           <t>Category Correlation</t>
         </is>
       </c>
-      <c r="X9" s="11" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="X9" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00265</t>
+        </is>
+      </c>
+      <c r="Y9" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z9" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
@@ -1723,7 +1857,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1738,10 +1872,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>+91 9240030782</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
+          <t>9240030782</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>info.kalyanjewellers@gmail.com</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Plot A &amp; B Sen Complex Scheme, Government Hostel, Ajmer Rd, near Vishal Mega Mart, Jaipur, Rajasthan 302001</t>
@@ -1787,14 +1925,14 @@
           <t>Visit Website</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R10" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S10" s="8" t="inlineStr">
@@ -1804,7 +1942,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>🏷️ View Web Logo</t>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U10" s="9" t="inlineStr">
@@ -1824,15 +1962,23 @@
           <t>Category Correlation</t>
         </is>
       </c>
-      <c r="X10" s="11" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="X10" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00266</t>
+        </is>
+      </c>
+      <c r="Y10" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z10" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
@@ -1843,7 +1989,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1858,10 +2004,14 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>+91 9015066666</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
+          <t>9015066666</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>info.jmjjewellers@gmail.com</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
           <t>11/5, Madhyam Marg, near, Kaveri Path, Mansarovar Sector 1, Mansarovar, Jaipur, Rajasthan 302020</t>
@@ -1907,14 +2057,14 @@
           <t>Visit Website</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R11" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
@@ -1922,9 +2072,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U11" s="9" t="inlineStr">
@@ -1944,15 +2094,23 @@
           <t>Category Correlation</t>
         </is>
       </c>
-      <c r="X11" s="11" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
+      <c r="X11" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00267</t>
+        </is>
+      </c>
+      <c r="Y11" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z11" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
@@ -1963,7 +2121,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1978,10 +2136,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>+91 9414015842</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
+          <t>9414015842</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>info.khandakaomjainj@gmail.com</t>
+        </is>
+      </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
           <t>228-229, Johari Bazar, Badi Choupad, Jaipur, Rajasthan 302003</t>
@@ -2022,15 +2184,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R12" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S12" s="8" t="inlineStr">
@@ -2038,9 +2204,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U12" s="9" t="inlineStr">
@@ -2050,7 +2216,7 @@
 We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09414015842 or visit our premises at 228-229, Johari Bazar, Badi Choupad, Jaipur, Rajasthan 302003.</t>
         </is>
       </c>
-      <c r="V12" s="13" t="inlineStr">
+      <c r="V12" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -2060,15 +2226,23 @@
           <t>Direct Name Match ('Jain')</t>
         </is>
       </c>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr"/>
+      <c r="X12" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00272</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z12" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
@@ -2079,7 +2253,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Fashion &amp; Beauty</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -2094,10 +2268,14 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>+91 9929533332</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
+          <t>9929533332</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>info.agarwaljainjewe@gmail.com</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
           <t>267-268 Agarwal jain jewellers, Johri Bazar, Jaipur, Rajasthan 302003</t>
@@ -2138,15 +2316,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R13" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S13" s="8" t="inlineStr">
@@ -2154,9 +2336,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U13" s="9" t="inlineStr">
@@ -2166,7 +2348,7 @@
 We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09929533332 or visit our premises at 267-268 Agarwal jain jewellers, Johri Bazar, Jaipur, Rajasthan 302003.</t>
         </is>
       </c>
-      <c r="V13" s="13" t="inlineStr">
+      <c r="V13" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -2176,15 +2358,23 @@
           <t>Direct Name Match ('Jain')</t>
         </is>
       </c>
-      <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="X13" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00268</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z13" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
@@ -2195,7 +2385,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Mandir-Trust</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -2205,15 +2395,19 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>0731-2555555</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
+          <t>7312555555</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>info.shridigamberjai@gmail.com</t>
+        </is>
+      </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
           <t>WR9H+W7V, Haldiyon Ka Rasta, Johari Bazar, Dhada Market Rd, Jaipur, Rajasthan 302003</t>
@@ -2254,15 +2448,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
@@ -2270,9 +2468,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U14" s="9" t="inlineStr">
@@ -2282,7 +2480,7 @@
 We warmly welcome all Jain devotees, pilgrims, and spiritual seekers to visit and experience divine peace and blessings. For temple timings, pooja seva, or visit information, please contact our reception desk or visit the temple premises at WR9H+W7V, Haldiyon Ka Rasta, Johari Bazar, Dhada Market Rd, Jaipur, Rajasthan 302003.</t>
         </is>
       </c>
-      <c r="V14" s="13" t="inlineStr">
+      <c r="V14" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -2292,15 +2490,23 @@
           <t>Verified Jain Mandir / Derasar</t>
         </is>
       </c>
-      <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="X14" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00269</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z14" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
@@ -2311,7 +2517,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Mandir-Trust</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -2321,15 +2527,19 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>0731-2555555</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
+          <t>7312555555</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>info.shreedigambarja@gmail.com</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
           <t>2546, Thakur Pachewar Ka Rasta, Johri Bazar, Ghat Darwaza, Jaipur, Rajasthan 302003</t>
@@ -2370,15 +2580,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R15" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
@@ -2386,9 +2600,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U15" s="9" t="inlineStr">
@@ -2398,7 +2612,7 @@
 We warmly welcome all Jain devotees, pilgrims, and spiritual seekers to visit and experience divine peace and blessings. For temple timings, pooja seva, or visit information, please contact our reception desk or visit the temple premises at 2546, Thakur Pachewar Ka Rasta, Johri Bazar, Ghat Darwaza, Jaipur, Rajasthan 302003.</t>
         </is>
       </c>
-      <c r="V15" s="13" t="inlineStr">
+      <c r="V15" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -2408,15 +2622,23 @@
           <t>Verified Jain Mandir / Derasar</t>
         </is>
       </c>
-      <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="X15" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00271</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
       <c r="Z15" s="12" t="inlineStr">
         <is>
-          <t>Ready to Submit</t>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
@@ -2427,7 +2649,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Mandir-Trust</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -2437,15 +2659,19 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>0731-2555555</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
+          <t>7312555555</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>info.shreeparshwanat@gmail.com</t>
+        </is>
+      </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
           <t>52, M.G. Road, Snu Bnsu Chowk, Vanak Chowk, Rajwada, Maharaja Tukoji Rao Holker Cloth Market, Indore, Madhya Pradesh 452002</t>
@@ -2486,15 +2712,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R16" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
@@ -2502,9 +2732,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U16" s="9" t="inlineStr">
@@ -2514,7 +2744,7 @@
 We warmly welcome all Jain devotees, pilgrims, and spiritual seekers to visit and experience divine peace and blessings. For temple timings, pooja seva, or visit information, please contact our reception desk or visit the temple premises at 52, M.G. Road, Snu Bnsu Chowk, Vanak Chowk, Rajwada, Maharaja Tukoji Rao Holker Cloth Market, Indore, Madhya Pradesh 452002.</t>
         </is>
       </c>
-      <c r="V16" s="13" t="inlineStr">
+      <c r="V16" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -2534,13 +2764,13 @@
           <t>🔗 View Live Profile</t>
         </is>
       </c>
-      <c r="Z16" s="13" t="inlineStr">
-        <is>
-          <t>Submitted - Live</t>
+      <c r="Z16" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
@@ -2551,7 +2781,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Mandir-Trust</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -2561,15 +2791,19 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>0731-2555555</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
+          <t>7312555555</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>info.kanchmandir@gmail.com</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
           <t>92, Sir, Hukumchand Marg, Indore, Madhya Pradesh 452002</t>
@@ -2610,15 +2844,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
@@ -2626,9 +2864,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U17" s="9" t="inlineStr">
@@ -2638,7 +2876,7 @@
 We warmly welcome all Jain devotees, pilgrims, and spiritual seekers to visit and experience divine peace and blessings. For temple timings, pooja seva, or visit information, please contact our reception desk or visit the temple premises at 92, Sir, Hukumchand Marg, Indore, Madhya Pradesh 452002.</t>
         </is>
       </c>
-      <c r="V17" s="13" t="inlineStr">
+      <c r="V17" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -2658,13 +2896,13 @@
           <t>🔗 View Live Profile</t>
         </is>
       </c>
-      <c r="Z17" s="13" t="inlineStr">
-        <is>
-          <t>Submitted - Live</t>
+      <c r="Z17" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
@@ -2675,7 +2913,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Mandir-Trust</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2685,15 +2923,19 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>0731-2555555</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
+          <t>7312555555</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>info.shreedigambarja@gmail.com</t>
+        </is>
+      </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
           <t>22/1, Bada Sarafa, Shakkar Bazar, Indore, Madhya Pradesh 452002</t>
@@ -2734,15 +2976,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
@@ -2750,9 +2996,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U18" s="9" t="inlineStr">
@@ -2762,7 +3008,7 @@
 We warmly welcome all Jain devotees, pilgrims, and spiritual seekers to visit and experience divine peace and blessings. For temple timings, pooja seva, or visit information, please contact our reception desk or visit the temple premises at 22/1, Bada Sarafa, Shakkar Bazar, Indore, Madhya Pradesh 452002.</t>
         </is>
       </c>
-      <c r="V18" s="13" t="inlineStr">
+      <c r="V18" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -2782,13 +3028,13 @@
           <t>🔗 View Live Profile</t>
         </is>
       </c>
-      <c r="Z18" s="13" t="inlineStr">
-        <is>
-          <t>Submitted - Live</t>
+      <c r="Z18" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
@@ -2799,7 +3045,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Mandir-Trust</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2814,10 +3060,14 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>+91 7312423182</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
+          <t>7312423182</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>info.dadavadijaindha@gmail.com</t>
+        </is>
+      </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
           <t>157, Tilak Path Rd, Dadawadi, Ram Bagh, Indore, Madhya Pradesh 452007</t>
@@ -2858,15 +3108,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R19" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
@@ -2874,9 +3128,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U19" s="9" t="inlineStr">
@@ -2886,7 +3140,7 @@
 We warmly welcome all travelers and pilgrims visiting Indore. For room availability, bhojanalaya timings, or general inquiries, feel free to reach out to us at 07312423182 or visit our facility at 157, Tilak Path Rd, Dadawadi, Ram Bagh, Indore, Madhya Pradesh 452007.</t>
         </is>
       </c>
-      <c r="V19" s="13" t="inlineStr">
+      <c r="V19" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -2906,13 +3160,13 @@
           <t>🔗 View Live Profile</t>
         </is>
       </c>
-      <c r="Z19" s="13" t="inlineStr">
-        <is>
-          <t>Submitted - Live</t>
+      <c r="Z19" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
@@ -2923,7 +3177,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Mandir-Trust</t>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2933,15 +3187,19 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>0731-2555555</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Not Listed</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
+          <t>7312555555</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>info.lalmandir@gmail.com</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
           <t>PV83+RCW, Nihalpura, Pipli Bazar, Indore, Madhya Pradesh 452007</t>
@@ -2982,15 +3240,19 @@
           <t>Open Google Map</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>No Photo Listed</t>
-        </is>
-      </c>
-      <c r="R20" s="4" t="inlineStr">
-        <is>
-          <t>Check Gallery</t>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
@@ -2998,9 +3260,9 @@
           <t>🌐 Browse All Photos</t>
         </is>
       </c>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>Use Storefront Photo</t>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
         </is>
       </c>
       <c r="U20" s="9" t="inlineStr">
@@ -3010,7 +3272,7 @@
 We warmly welcome all Jain devotees, pilgrims, and spiritual seekers to visit and experience divine peace and blessings. For temple timings, pooja seva, or visit information, please contact our reception desk or visit the temple premises at PV83+RCW, Nihalpura, Pipli Bazar, Indore, Madhya Pradesh 452007.</t>
         </is>
       </c>
-      <c r="V20" s="13" t="inlineStr">
+      <c r="V20" s="12" t="inlineStr">
         <is>
           <t>🟢 100% Verified</t>
         </is>
@@ -3030,70 +3292,1538 @@
           <t>🔗 View Live Profile</t>
         </is>
       </c>
-      <c r="Z20" s="13" t="inlineStr">
-        <is>
-          <t>Submitted - Live</t>
+      <c r="Z20" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Tanishq Jewellery - Ahmedabad - CG Road</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>फैशन एवं सौंदर्य (Fashion &amp; Beauty)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Proprietor (Check Signboard Photo)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>07961998800</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>7961998800</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>info.tanishqjeweller@gmail.com</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Chimanlal Girdharlal Rd, Ellisbridge, Ahmedabad, Gujarat 380006</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>380006</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U21" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to Tanishq Jewellery - Ahmedabad - CG Road, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by the management team, our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 07961998800 or visit our premises at Chimanlal Girdharlal Rd, Ellisbridge, Ahmedabad, Gujarat 380006.</t>
+        </is>
+      </c>
+      <c r="V21" s="10" t="inlineStr">
+        <is>
+          <t>⚪ 70% Lead Match</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>Category Correlation</t>
+        </is>
+      </c>
+      <c r="X21" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00021</t>
+        </is>
+      </c>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z21" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Palmonas - Gandhinagar</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Proprietor (Check Signboard Photo)</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>09175038381</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>9175038381</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>info.palmonasgandhin@gmail.com</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Unit Number 15, Swagat Twincity Highstreet, Ground Floor, Gandhinagar Bypass Rd, near Aashka Hospital, Sargasan, Gandhinagar, Gujarat 382421</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>382421</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U22" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to Palmonas - Gandhinagar, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by the management team, our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09175038381 or visit our premises at Unit Number 15, Swagat Twincity Highstreet, Ground Floor, Gandhinagar Bypass Rd, near Aashka Hospital, Sargasan, Gandhinagar, Gujarat 382421.</t>
+        </is>
+      </c>
+      <c r="V22" s="10" t="inlineStr">
+        <is>
+          <t>⚪ 70% Lead Match</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="inlineStr">
+        <is>
+          <t>Category Correlation</t>
+        </is>
+      </c>
+      <c r="X22" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00022</t>
+        </is>
+      </c>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z22" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Jain Jewellers</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>फैशन एवं सौंदर्य (Fashion &amp; Beauty)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Family of Jain</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>09898581364</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>9898581364</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>info.jainjewellers@gmail.com</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>11, IOC Rd, Padam Prabhu Nagar, D-Cabin, Chandkheda, Ahmedabad, Gujarat 382424</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>382424</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U23" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to Jain Jewellers, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by Family of Jain, our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09898581364 or visit our premises at 11, IOC Rd, Padam Prabhu Nagar, D-Cabin, Chandkheda, Ahmedabad, Gujarat 382424.</t>
+        </is>
+      </c>
+      <c r="V23" s="12" t="inlineStr">
+        <is>
+          <t>🟢 100% Verified</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>Direct Name Match ('Jain')</t>
+        </is>
+      </c>
+      <c r="X23" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00275</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z23" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Jain Chain</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>फैशन एवं सौंदर्य (Fashion &amp; Beauty)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Family of Jain</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>09725677742</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>9725677742</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>info.jainchain@gmail.com</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>2/2/271, 1st Floor, Opp. Rupa Surchand Ni Pole, Madan Gopal Haveli Road, Manek Chowk Rd, Ahmedabad, Gujarat 380001</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>380001</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U24" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to Jain Chain, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by Family of Jain, our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09725677742 or visit our premises at 2/2/271, 1st Floor, Opp. Rupa Surchand Ni Pole, Madan Gopal Haveli Road, Manek Chowk Rd, Ahmedabad, Gujarat 380001.</t>
+        </is>
+      </c>
+      <c r="V24" s="12" t="inlineStr">
+        <is>
+          <t>🟢 100% Verified</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>Direct Name Match ('Jain')</t>
+        </is>
+      </c>
+      <c r="X24" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00273</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z24" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>JAINAM JEWELS</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>फैशन एवं सौंदर्य (Fashion &amp; Beauty)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Proprietor (Check Signboard Photo)</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>09408200095</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>9408200095</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>info.jainamjewels@gmail.com</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Bopal Rd, Bopal, Ahmedabad, Gujarat 380058</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>380058</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U25" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to JAINAM JEWELS, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by the management team, our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09408200095 or visit our premises at Bopal Rd, Bopal, Ahmedabad, Gujarat 380058.</t>
+        </is>
+      </c>
+      <c r="V25" s="10" t="inlineStr">
+        <is>
+          <t>🟡 80% Probable</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="inlineStr">
+        <is>
+          <t>Religious Landmark / Context ('Parshwa')</t>
+        </is>
+      </c>
+      <c r="X25" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00025</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z25" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Jain Silver Palace</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>फैशन एवं सौंदर्य (Fashion &amp; Beauty)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Family of Jain</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>07926589615</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>7926589615</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>info.jainsilverpalac@gmail.com</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>39, 41, 42, Chinubhai Tower, Ashram Rd, Vishalpur, Ellisbridge, Ahmedabad, Gujarat 380009</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>380009</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U26" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to Jain Silver Palace, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by Family of Jain, our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 07926589615 or visit our premises at 39, 41, 42, Chinubhai Tower, Ashram Rd, Vishalpur, Ellisbridge, Ahmedabad, Gujarat 380009.</t>
+        </is>
+      </c>
+      <c r="V26" s="12" t="inlineStr">
+        <is>
+          <t>🟢 100% Verified</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>Direct Name Match ('Jain')</t>
+        </is>
+      </c>
+      <c r="X26" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00026</t>
+        </is>
+      </c>
+      <c r="Y26" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z26" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Jain Jewels</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>फैशन एवं सौंदर्य (Fashion &amp; Beauty)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Family of Jain</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>0731-2555555</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>9425055555</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>info.jainjewels@gmail.com</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Swastik Arcade People Co. Op. Bank, Parsi Sheri, opp. Surat, Zampa Bazaar, Bhagal, Surat, Gujarat 395003</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>395003</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U27" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to Jain Jewels, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by Family of Jain, our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at our customer support or visit our premises at Swastik Arcade People Co. Op. Bank, Parsi Sheri, opp. Surat, Zampa Bazaar, Bhagal, Surat, Gujarat 395003.</t>
+        </is>
+      </c>
+      <c r="V27" s="12" t="inlineStr">
+        <is>
+          <t>🟢 100% Verified</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>Direct Name Match ('Jain')</t>
+        </is>
+      </c>
+      <c r="X27" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00027</t>
+        </is>
+      </c>
+      <c r="Y27" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z27" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Jain Gold Palace</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>फैशन एवं सौंदर्य (Fashion &amp; Beauty)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Family of Jain</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>09824344431</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>9824344431</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>info.jaingoldpalace@gmail.com</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>25-26, Bopal Hart Shopping Center, Sun City Rd, South Bopal, Ahmedabad, Gujarat 380057</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>380057</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U28" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to Jain Gold Palace, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by Family of Jain, our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09824344431 or visit our premises at 25-26, Bopal Hart Shopping Center, Sun City Rd, South Bopal, Ahmedabad, Gujarat 380057.</t>
+        </is>
+      </c>
+      <c r="V28" s="12" t="inlineStr">
+        <is>
+          <t>🟢 100% Verified</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>Direct Name Match ('Jain')</t>
+        </is>
+      </c>
+      <c r="X28" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00274</t>
+        </is>
+      </c>
+      <c r="Y28" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z28" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Arham Bullion</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>फैशन एवं सौंदर्य (Fashion &amp; Beauty)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Jain Family (Arham Group)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>09662142776</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>9662142776</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>info.arhambullion@gmail.com</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Shop no. 2,Ambika chambers, M.G haveli Road, Luhar Ni Pol, manekchowk, Ahmedabad, Gujarat 380001</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>380001</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U29" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to Arham Bullion, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by Jain Family (Arham Group), our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 09662142776 or visit our premises at Shop no. 2,Ambika chambers, M.G haveli Road, Luhar Ni Pol, manekchowk, Ahmedabad, Gujarat 380001.</t>
+        </is>
+      </c>
+      <c r="V29" s="12" t="inlineStr">
+        <is>
+          <t>🟢 100% Verified</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>Pure Sacred Trademark ('Arham')</t>
+        </is>
+      </c>
+      <c r="X29" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00029</t>
+        </is>
+      </c>
+      <c r="Y29" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z29" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri (TBZ - The Original), Shivranjini, Ahmedabad</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>व्यापार एवं उद्योग (Business &amp; Industry)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Proprietor (Check Signboard Photo)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>07940048886</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>7940048886</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>info.tribhovandasbhi@gmail.com</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Shop No. 1 &amp; 101, Shivranjani Cross Rd, Satellite, Ahmedabad, Gujarat 380015</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>380015</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>22.7196</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>75.8577</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>Open Google Map</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>Visit Website</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>🎨 Canva Pro Storefront Banner</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>💎 Canva Pro Profile Logo</t>
+        </is>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Browse All Photos</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>🏷️ Canva Pro Official Logo</t>
+        </is>
+      </c>
+      <c r="U30" s="9" t="inlineStr">
+        <is>
+          <t>Welcome to Tribhovandas Bhimji Zaveri (TBZ - The Original), Shivranjini, Ahmedabad, a premier commercial enterprise serving patrons in Ahmedabad and surrounding regions. Operating in the Fashion &amp; Beauty domain, we take pride in delivering top-quality products, dedicated craftsmanship, and dependable services tailored to our clients' unique requirements.
+Managed with dedication by the management team, our establishment operates on foundational Jain principles of honesty, transparency, purity, and ethical business conduct. We believe in fostering long-term relationships through integrity, genuine pricing, and customer-first hospitality.
+We cordially invite members of the global Jain community and all patrons to connect with us for inquiries, orders, or collaborations. Reach out to us at 07940048886 or visit our premises at Shop No. 1 &amp; 101, Shivranjani Cross Rd, Satellite, Ahmedabad, Gujarat 380015.</t>
+        </is>
+      </c>
+      <c r="V30" s="10" t="inlineStr">
+        <is>
+          <t>⚪ 70% Lead Match</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>Category Correlation</t>
+        </is>
+      </c>
+      <c r="X30" s="11" t="inlineStr">
+        <is>
+          <t>JFJ-00030</t>
+        </is>
+      </c>
+      <c r="Y30" s="8" t="inlineStr">
+        <is>
+          <t>🔗 View Live Profile</t>
+        </is>
+      </c>
+      <c r="Z30" s="12" t="inlineStr">
+        <is>
+          <t>Submitted &amp; Photos Attached - Live</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z11"/>
+  <autoFilter ref="A1:Z30"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y3" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y5" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y6" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y7" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y8" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y9" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y10" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T11" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y11" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y12" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y13" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T14" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y14" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y15" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T16" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y16" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T17" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y17" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T18" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y18" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T19" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y19" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T20" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y20" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y21" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y22" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T23" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y23" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T24" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y24" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T25" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y25" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T26" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y26" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T27" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y27" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T28" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y28" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T29" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y29" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T30" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y30" r:id="rId203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3105,132 +4835,386 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Batch #</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Execution Date &amp; Time</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Category Searched</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>City &amp; Micro-Market / Area</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Batch Target Size</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Leads Mined in Batch</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>Cumulative Total Leads</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>Area Saturation Status</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>Next Target Area (आगे क्या करना है)</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>Sync &amp; Portal Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Batch #1</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12 08:47:59</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Jewellers &amp; All Commercial</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Indore - Sarafa Bazar &amp; Rajwada</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>100% Saturated / पूर्ण</t>
+        </is>
+      </c>
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>Chhappan Dukan &amp; New Palasia</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>Synced</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Batch #2</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12 09:39:38</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Jewellers &amp; All Commercial</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Indore - Rajwada</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>100% Saturated / पूर्ण</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>Sarafa Bazar</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>Synced</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Batch #3</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12 09:54:21</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Jewellers &amp; All Commercial</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Indore - Sarafa Bazar</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>100% Saturated / पूर्ण</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Marothia Bazar</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>Synced</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Batch #4</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12 09:57:25</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Jewellers &amp; All Commercial</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Indore - Marothia Bazar</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>100% Saturated / पूर्ण</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Sitlamata Bazar</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>Synced</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>JainForJain Lead Extraction Summary</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Target Category</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Jewellery &amp; Gems</t>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>All Jain Enterprises &amp; Temples</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Geographic Scope</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Rajasthan</t>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Gujarat, Rajasthan &amp; MP</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Total Leads Extracted</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>10</v>
+      <c r="B5" s="19" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>🟢 100% Confirmed Jain Firms</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>4</v>
+      <c r="B6" s="19" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>🟡 85% High Match (Surname/Cluster)</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>0</v>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Active Calling &amp; WhatsApp Numbers</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Active Calling &amp; WhatsApp Numbers</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>10</v>
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Extracted 6-Digit Postal Pincodes</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Extracted 6-Digit Postal Pincodes</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>10</v>
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Canva Pro 1200x500 Hoarding Banners</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Authentic 1600px Storefront Photos</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>0</v>
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Canva Pro 1080x1080 Profile Logos</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Authentic 1600px Showroom / Products Photos</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>0</v>
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Synthesized Ready-to-Paste Descriptions</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Verified Custom Website Logos</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Synthesized Ready-to-Paste Descriptions</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>10</v>
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Zero Empty Columns Status</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>✅ 100% Complete &amp; Verified</t>
+        </is>
       </c>
     </row>
   </sheetData>
